--- a/data/trans_bre/POLIPATOLOGIA_Lim_5-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_5-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 8,98</t>
+          <t>0,38; 9,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 14,21</t>
+          <t>4,72; 14,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,89</t>
+          <t>0,81; 5,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 342,35</t>
+          <t>-2,48; 400,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,08; 658,49</t>
+          <t>76,62; 696,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,18; 513,71</t>
+          <t>15,66; 421,49</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,06</t>
+          <t>0,69; 7,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,14</t>
+          <t>2,6; 7,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,0</t>
+          <t>4,77; 11,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 209,16</t>
+          <t>5,91; 217,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>131,25; 1745,05</t>
+          <t>120,62; 1669,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,65; 302,79</t>
+          <t>59,22; 311,85</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 9,0</t>
+          <t>1,38; 9,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,0</t>
+          <t>1,3; 7,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 8,99</t>
+          <t>0,43; 9,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,19; 539,36</t>
+          <t>20,66; 689,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,28; 811,23</t>
+          <t>42,57; 1204,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 96,61</t>
+          <t>3,05; 101,68</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 13,66</t>
+          <t>5,35; 13,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 12,2</t>
+          <t>3,72; 11,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 7,39</t>
+          <t>-3,58; 7,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,77; 537,3</t>
+          <t>83,54; 499,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,14; 377,17</t>
+          <t>47,86; 360,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 94,4</t>
+          <t>-27,05; 92,33</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 15,84</t>
+          <t>2,91; 15,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 10,62</t>
+          <t>1,1; 11,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,18</t>
+          <t>-0,78; 10,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,7; 274,22</t>
+          <t>23,13; 274,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 436,85</t>
+          <t>5,24; 411,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 252,11</t>
+          <t>-5,91; 247,84</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 5,3</t>
+          <t>-2,58; 5,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 7,88</t>
+          <t>0,95; 7,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 15,37</t>
+          <t>5,24; 15,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 167,37</t>
+          <t>-41,61; 174,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 526,38</t>
+          <t>10,76; 559,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,66; 120,89</t>
+          <t>29,97; 122,78</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 9,36</t>
+          <t>3,92; 9,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,9</t>
+          <t>2,17; 7,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 13,71</t>
+          <t>-1,62; 13,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107,56; 532,16</t>
+          <t>103,32; 512,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,26; 264,39</t>
+          <t>39,17; 269,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 181,49</t>
+          <t>-14,91; 177,63</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,12</t>
+          <t>3,72; 7,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,25; 9,4</t>
+          <t>4,52; 9,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,09</t>
+          <t>6,52; 12,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131,44; 795,32</t>
+          <t>147,72; 755,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>102,13; 412,8</t>
+          <t>110,6; 414,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>137,85; 735,59</t>
+          <t>137,81; 670,01</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,86</t>
+          <t>4,57; 6,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,03</t>
+          <t>4,72; 7,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,97</t>
+          <t>4,63; 9,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>111,2; 217,98</t>
+          <t>113,53; 227,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>132,22; 256,47</t>
+          <t>131,62; 257,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68,6; 159,89</t>
+          <t>68,95; 162,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_Lim_5-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_5-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>3,36</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>137,57%</t>
+          <t>135,12%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 9,02</t>
+          <t>0,28; 8,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 14,69</t>
+          <t>4,41; 14,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,91</t>
+          <t>0,99; 5,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 400,51</t>
+          <t>-6,17; 372,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>76,62; 696,23</t>
+          <t>65,66; 647,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,66; 421,49</t>
+          <t>11,36; 384,1</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,08</t>
+          <t>7,61</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>158,96%</t>
+          <t>143,38%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,34</t>
+          <t>0,67; 7,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,11</t>
+          <t>2,28; 6,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,43</t>
+          <t>4,54; 10,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 217,73</t>
+          <t>1,68; 206,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>120,62; 1669,2</t>
+          <t>115,25; 1508,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,22; 311,85</t>
+          <t>60,28; 285,14</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 9,31</t>
+          <t>1,75; 9,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,56</t>
+          <t>1,2; 7,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 9,03</t>
+          <t>1,06; 8,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,66; 689,76</t>
+          <t>19,45; 712,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,57; 1204,28</t>
+          <t>26,45; 966,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 101,68</t>
+          <t>7,42; 105,72</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>6,03</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 13,25</t>
+          <t>5,36; 13,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 11,88</t>
+          <t>3,45; 12,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 7,07</t>
+          <t>1,56; 10,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83,54; 499,14</t>
+          <t>89,45; 469,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>47,86; 360,97</t>
+          <t>51,41; 377,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 92,33</t>
+          <t>11,07; 159,46</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>7,88</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>148,8%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 15,75</t>
+          <t>3,78; 16,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,22</t>
+          <t>0,97; 11,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 10,02</t>
+          <t>4,08; 11,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,13; 274,6</t>
+          <t>24,69; 292,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 411,14</t>
+          <t>7,42; 395,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 247,84</t>
+          <t>52,74; 314,7</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,24</t>
+          <t>10,37</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 5,26</t>
+          <t>-2,52; 5,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,98</t>
+          <t>0,48; 7,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,24; 15,13</t>
+          <t>5,23; 15,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,61; 174,13</t>
+          <t>-37,88; 174,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,76; 559,37</t>
+          <t>2,29; 539,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,97; 122,78</t>
+          <t>28,34; 125,48</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,75</t>
+          <t>12,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>156,36%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,11</t>
+          <t>3,91; 9,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,82</t>
+          <t>2,41; 7,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 13,67</t>
+          <t>9,69; 16,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>103,32; 512,21</t>
+          <t>107,43; 555,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,17; 269,38</t>
+          <t>42,48; 275,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 177,63</t>
+          <t>96,35; 236,54</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9,17</t>
+          <t>7,3</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>283,21%</t>
+          <t>170,18%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,72</t>
+          <t>3,62; 7,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,52; 9,61</t>
+          <t>4,45; 9,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,52; 12,12</t>
+          <t>4,95; 9,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147,72; 755,02</t>
+          <t>143,84; 791,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>110,6; 414,21</t>
+          <t>98,59; 407,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>137,81; 670,01</t>
+          <t>86,61; 275,19</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>8,05</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>109,25%</t>
+          <t>115,23%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,87</t>
+          <t>4,52; 7,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,08</t>
+          <t>4,67; 7,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,09</t>
+          <t>6,76; 9,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>113,53; 227,32</t>
+          <t>108,48; 224,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>131,62; 257,54</t>
+          <t>132,91; 263,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68,95; 162,33</t>
+          <t>88,99; 146,03</t>
         </is>
       </c>
     </row>
